--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B767F49-32C5-468B-A84D-415208E8DEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF140F85-0320-4F01-B1E1-579A48C6D113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Activity" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF140F85-0320-4F01-B1E1-579A48C6D113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58042F0-2983-4FFC-ADB2-ED937AF9813D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58042F0-2983-4FFC-ADB2-ED937AF9813D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7257344-47D5-4A47-A8B9-134F84F2BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7257344-47D5-4A47-A8B9-134F84F2BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DCBCFE-06D0-4D11-AD77-969A9F355F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -841,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="D5" s="2">
         <v>50</v>

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DCBCFE-06D0-4D11-AD77-969A9F355F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C9A47A-87C5-41D5-8623-53A920CDE43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C9A47A-87C5-41D5-8623-53A920CDE43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A4CA0E-8236-46D8-BA66-6852FCEB9C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A4CA0E-8236-46D8-BA66-6852FCEB9C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC6969C-B9CA-4574-AA47-7311FE73D1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Activity" sheetId="1" r:id="rId1"/>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>50000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC6969C-B9CA-4574-AA47-7311FE73D1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDA6460-D561-4EC7-81A5-1B183ABAD1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Activity" sheetId="1" r:id="rId1"/>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>700000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDA6460-D561-4EC7-81A5-1B183ABAD1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ACF559-2467-4E1D-B69F-9903A3BE6359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,7 +885,7 @@
         <v>-10</v>
       </c>
       <c r="H6" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ACF559-2467-4E1D-B69F-9903A3BE6359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDF2AB1-77DD-4486-8A22-4AC4041FFD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Activity" sheetId="1" r:id="rId1"/>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>70000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_Activity.xlsx
+++ b/JsonConverter/ExcelFiles/0_Activity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDF2AB1-77DD-4486-8A22-4AC4041FFD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E4827D-8DC1-4699-9B2D-2E3D174C57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -844,7 +844,7 @@
         <v>300</v>
       </c>
       <c r="D5" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -870,7 +870,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D6" s="12">
         <v>0</v>
